--- a/wits_cache/wits_PRT_2024_E_070200.xlsx
+++ b/wits_cache/wits_PRT_2024_E_070200.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="SpreadsheetGear 7.1.1.120"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vincent.Frippiat\Downloads\testtrae\wits_cache\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A065B14-FEDC-49E4-8F6E-26AE18D311A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18075" windowHeight="9900" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="By-HS6Product" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="40001"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="72">
   <si>
     <t>Reporter</t>
   </si>
@@ -105,15 +111,6 @@
   </si>
   <si>
     <t>1.9443e+006</t>
-  </si>
-  <si>
-    <t>Bunkers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            513.31</t>
-  </si>
-  <si>
-    <t>294246</t>
   </si>
   <si>
     <t>Italy</t>
@@ -245,136 +242,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="17">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -403,6 +278,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -690,636 +575,607 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.13671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.41015625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.4140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.8515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.98828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.4140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row>
-      <c t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c t="s">
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c t="s">
+      <c r="H3" t="s">
         <v>20</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c t="s">
+      <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c t="s">
+      <c r="H4" t="s">
         <v>23</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c t="s">
+      <c r="G5" t="s">
         <v>25</v>
       </c>
-      <c t="s">
+      <c r="H5" t="s">
         <v>26</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c t="s">
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c t="s">
+      <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
         <v>30</v>
       </c>
-      <c t="s">
+      <c r="G7" t="s">
         <v>31</v>
       </c>
-      <c t="s">
+      <c r="H7" t="s">
         <v>32</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
         <v>33</v>
       </c>
-      <c t="s">
+      <c r="G8" t="s">
         <v>34</v>
       </c>
-      <c t="s">
+      <c r="H8" t="s">
         <v>35</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
         <v>36</v>
       </c>
-      <c t="s">
+      <c r="G9" t="s">
         <v>37</v>
       </c>
-      <c t="s">
+      <c r="H9" t="s">
         <v>38</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
         <v>39</v>
       </c>
-      <c t="s">
+      <c r="G10" t="s">
         <v>40</v>
       </c>
-      <c t="s">
+      <c r="H10" t="s">
         <v>41</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
         <v>42</v>
       </c>
-      <c t="s">
+      <c r="G11" t="s">
         <v>43</v>
       </c>
-      <c t="s">
+      <c r="H11" t="s">
         <v>44</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
         <v>45</v>
       </c>
-      <c t="s">
+      <c r="G12" t="s">
         <v>46</v>
       </c>
-      <c t="s">
+      <c r="H12" t="s">
         <v>47</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
         <v>48</v>
       </c>
-      <c t="s">
+      <c r="G13" t="s">
         <v>49</v>
       </c>
-      <c t="s">
+      <c r="H13" t="s">
         <v>50</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
         <v>51</v>
       </c>
-      <c t="s">
+      <c r="G14" t="s">
         <v>52</v>
       </c>
-      <c t="s">
+      <c r="H14" t="s">
         <v>53</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
         <v>54</v>
       </c>
-      <c t="s">
+      <c r="G15" t="s">
         <v>55</v>
       </c>
-      <c t="s">
+      <c r="H15" t="s">
         <v>56</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
         <v>57</v>
       </c>
-      <c t="s">
+      <c r="G16" t="s">
         <v>58</v>
       </c>
-      <c t="s">
+      <c r="H16" t="s">
         <v>59</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
         <v>60</v>
       </c>
-      <c t="s">
+      <c r="G17" t="s">
         <v>61</v>
       </c>
-      <c t="s">
+      <c r="H17" t="s">
         <v>62</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
         <v>63</v>
       </c>
-      <c t="s">
+      <c r="G18" t="s">
         <v>64</v>
       </c>
-      <c t="s">
+      <c r="H18" t="s">
         <v>65</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
         <v>66</v>
       </c>
-      <c t="s">
+      <c r="G19" t="s">
         <v>67</v>
       </c>
-      <c t="s">
+      <c r="H19" t="s">
         <v>68</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
         <v>69</v>
       </c>
-      <c t="s">
+      <c r="G20" t="s">
         <v>70</v>
       </c>
-      <c t="s">
+      <c r="H20" t="s">
         <v>71</v>
       </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>9</v>
-      </c>
-      <c t="s">
-        <v>10</v>
-      </c>
-      <c t="s">
-        <v>11</v>
-      </c>
-      <c t="s">
-        <v>12</v>
-      </c>
-      <c t="s">
-        <v>13</v>
-      </c>
-      <c t="s">
-        <v>72</v>
-      </c>
-      <c t="s">
-        <v>73</v>
-      </c>
-      <c t="s">
-        <v>74</v>
-      </c>
-      <c t="s">
+      <c r="I20" t="s">
         <v>17</v>
       </c>
     </row>
